--- a/DateBase/orders/Dang Nguyen 195_2026-3-17.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-3-17.xlsx
@@ -865,6 +865,9 @@
       <c r="C51" t="str">
         <v>420_松虫草QQ糖_scabiosa white pink_undefined_1bunch</v>
       </c>
+      <c r="F51" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -923,7 +926,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0610155312914832586335111578040151558153014105106312108510105355351022420</v>
+        <v>0610155312914832586335111578040151558153014105106312108510105355351022425</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-3-17.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-3-17.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L81"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -869,9 +869,268 @@
         <v>5</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>1</v>
+      </c>
+      <c r="C52" t="str">
+        <v>420_松虫草QQ糖_scabiosa white pink_undefined_1bunch</v>
+      </c>
+      <c r="F52" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F53" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+      <c r="F54" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>314_松虫草花边黑_scabiosa_undefined_1bunch</v>
+      </c>
+      <c r="F55" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
+      </c>
+      <c r="F56" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>469_络新妇粉_Astilbe pink_undefined_1bunch</v>
+      </c>
+      <c r="F57" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>643_巧克力秋英_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F58" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>878_玛格丽特粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F59" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2</v>
+      </c>
+      <c r="C60" t="str">
+        <v>859_喷色小米果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F60" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>726_鸢尾叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F61" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F62" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>1</v>
+      </c>
+      <c r="C63" t="str">
+        <v>775_海芋黑_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F63" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="str">
+        <v>745_海芋红_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F64" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>2</v>
+      </c>
+      <c r="C65" t="str">
+        <v>863_干花文竹白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F65" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" t="str">
+        <v>629_干花蓬莱松_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F66" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" xml:space="preserve">
+      <c r="A67" t="str">
+        <v>3</v>
+      </c>
+      <c r="C67" t="str" xml:space="preserve">
+        <v xml:space="preserve">553_嘉兰百合
+multi-colors_ gloriosa_undefined_1bunch</v>
+      </c>
+      <c r="F67" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" xml:space="preserve">
+      <c r="A68" t="str">
+        <v>4</v>
+      </c>
+      <c r="C68" t="str" xml:space="preserve">
+        <v xml:space="preserve">542_吊米 红_hanging amaranthus
+red_undefined_1bunch</v>
+      </c>
+      <c r="F68" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" xml:space="preserve">
+      <c r="C69" t="str" xml:space="preserve">
+        <v xml:space="preserve">448_吊米 绿_hanging amaranthus
+green_undefined_1bunch</v>
+      </c>
+      <c r="F69" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" t="str">
+        <v>577_腊梅白_wax white_undefined_1bunch</v>
+      </c>
+      <c r="F70" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="str">
+        <v>578_腊梅粉_wax pink_undefined_1bunch</v>
+      </c>
+      <c r="F71" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="C72" t="str">
+        <v>742_袋鼠爪绿_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F72" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" xml:space="preserve">
+      <c r="C73" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F73" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="C74" t="str">
+        <v>841_蝴蝶洋牡丹开炸了_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F74" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="C75" t="str">
+        <v>842_蝴蝶洋牡丹鲑鱼粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F75" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="C76" t="str">
+        <v>820_蝴蝶洋牡丹粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F76" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="C77" t="str">
+        <v>480_蝴蝶洋牡丹红_butterfly  Ranunculus_undefined_1bunch</v>
+      </c>
+      <c r="F77" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="C78" t="str">
+        <v>753_蝴蝶洋牡丹黄_butterfly  Ranunculus_undefined_1bunch</v>
+      </c>
+      <c r="F78" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="C79" t="str">
+        <v>752_蝴蝶洋牡丹橙_butterfly  Ranunculus_undefined_1bunch</v>
+      </c>
+      <c r="F79" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="C80" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F80" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" t="str">
+        <v>625_多丁紫蝴蝶_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L81"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -926,7 +1185,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0610155312914832586335111578040151558153014105106312108510105355351022425</v>
+        <v>06101553129148325863351115780401515581530141051063121085101053553510224251010101010610101010103330154561010530555333150</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-3-17.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-3-17.xlsx
@@ -1127,6 +1127,9 @@
       <c r="C81" t="str">
         <v>625_多丁紫蝴蝶_undefined_undefined_1bunch</v>
       </c>
+      <c r="F81" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1185,7 +1188,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>06101553129148325863351115780401515581530141051063121085101053553510224251010101010610101010103330154561010530555333150</v>
+        <v>061015531291483258633511157804015155815301410510631210851010535535102242510101010106101010101033301545610105305553331510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-3-17.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-3-17.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L92"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1131,9 +1131,103 @@
         <v>10</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>5</v>
+      </c>
+      <c r="C82" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F82" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="C83" t="str">
+        <v>738_鸢尾花蓝_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F83" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="C84" t="str">
+        <v>738_鸢尾花蓝_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F84" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="C85" t="str">
+        <v>774_紫娇花_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F85" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>6</v>
+      </c>
+      <c r="C86" t="str">
+        <v>648_洋牡丹河内_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F86" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="C87" t="str">
+        <v>649_洋牡丹樱花粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F87" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="C88" t="str">
+        <v>846_玛格丽特_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F88" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="C89" t="str">
+        <v>878_玛格丽特粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F89" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="C90" t="str">
+        <v>469_络新妇粉_Astilbe pink_undefined_1bunch</v>
+      </c>
+      <c r="F90" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="C91" t="str">
+        <v>551_铁线莲_Glematis_undefined_1bunch</v>
+      </c>
+      <c r="F91" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="C92" t="str">
+        <v>790_铁线莲粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F92" t="str">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L92"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1188,7 +1282,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>061015531291483258633511157804015155815301410510631210851010535535102242510101010106101010101033301545610105305553331510</v>
+        <v>061015531291483258633511157804015155815301410510631210851010535535102242510101010106101010101033301545610105305553331510301010101015155633</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-3-17.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-3-17.xlsx
@@ -1284,6 +1284,9 @@
       <c r="G2" t="str">
         <v>061015531291483258633511157804015155815301410510631210851010535535102242510101010106101010101033301545610105305553331510301010101015155633</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
